--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/07,09,26 Останкино КИ и ЗПФ/машина САП 13,09 Малахутин_ПРС_Донецк КИ/Заказ ЛП_Малахутин 13,09,26.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/07,09,26 Останкино КИ и ЗПФ/машина САП 13,09 Малахутин_ПРС_Донецк КИ/Заказ ЛП_Малахутин 13,09,26.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\09,09 Малахутин\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\09,26\07,09,26 Останкино КИ и ЗПФ\машина САП 13,09 Малахутин_ПРС_Донецк КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F03FC16-0C7F-4387-9613-09E74767FC83}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CBF09C6-6891-4483-9E70-60FFC827B5C2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6259,7 +6259,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BO1692"/>
@@ -6485,7 +6485,7 @@
       <c r="BN9" s="120"/>
       <c r="BO9" s="120"/>
     </row>
-    <row r="10" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="48"/>
       <c r="B10" s="43" t="s">
         <v>18</v>
@@ -6499,7 +6499,7 @@
       <c r="I10" s="43"/>
       <c r="J10" s="44"/>
     </row>
-    <row r="11" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:67" s="15" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58">
         <v>4561</v>
       </c>
@@ -6585,7 +6585,7 @@
       <c r="BN11" s="121"/>
       <c r="BO11" s="121"/>
     </row>
-    <row r="12" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:67" s="15" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="145">
         <v>7536</v>
       </c>
@@ -6673,7 +6673,7 @@
       <c r="BN12" s="121"/>
       <c r="BO12" s="121"/>
     </row>
-    <row r="13" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58">
         <v>5851</v>
       </c>
@@ -6761,7 +6761,7 @@
       <c r="BN13" s="121"/>
       <c r="BO13" s="121"/>
     </row>
-    <row r="14" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:67" s="15" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="58">
         <v>4813</v>
       </c>
@@ -6847,7 +6847,7 @@
       <c r="BN14" s="121"/>
       <c r="BO14" s="121"/>
     </row>
-    <row r="15" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:67" s="15" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58">
         <v>4574</v>
       </c>
@@ -7067,7 +7067,7 @@
       <c r="J18" s="29"/>
       <c r="L18" s="122"/>
     </row>
-    <row r="19" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58">
         <v>6861</v>
       </c>
@@ -7097,7 +7097,7 @@
       <c r="J19" s="29"/>
       <c r="L19" s="122"/>
     </row>
-    <row r="20" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="58">
         <v>6862</v>
       </c>
@@ -7161,7 +7161,7 @@
       </c>
       <c r="L21" s="122"/>
     </row>
-    <row r="22" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="58">
         <v>7334</v>
       </c>
@@ -7191,7 +7191,7 @@
       <c r="J22" s="29"/>
       <c r="L22" s="122"/>
     </row>
-    <row r="23" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58">
         <v>6325</v>
       </c>
@@ -7221,7 +7221,7 @@
       <c r="J23" s="29"/>
       <c r="L23" s="122"/>
     </row>
-    <row r="24" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="58">
         <v>8014</v>
       </c>
@@ -7307,7 +7307,7 @@
       <c r="BN24" s="122"/>
       <c r="BO24" s="122"/>
     </row>
-    <row r="25" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="145">
         <v>7632</v>
       </c>
@@ -7395,7 +7395,7 @@
       <c r="BN25" s="122"/>
       <c r="BO25" s="122"/>
     </row>
-    <row r="26" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="145">
         <v>7523</v>
       </c>
@@ -7483,7 +7483,7 @@
       <c r="BN26" s="122"/>
       <c r="BO26" s="122"/>
     </row>
-    <row r="27" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="147">
         <v>6340</v>
       </c>
@@ -7515,7 +7515,7 @@
       </c>
       <c r="L27" s="122"/>
     </row>
-    <row r="28" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="147">
         <v>6341</v>
       </c>
@@ -7611,7 +7611,7 @@
       <c r="J30" s="61"/>
       <c r="L30" s="122"/>
     </row>
-    <row r="31" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="58">
         <v>7343</v>
       </c>
@@ -7729,7 +7729,7 @@
       <c r="BN32" s="122"/>
       <c r="BO32" s="122"/>
     </row>
-    <row r="33" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="58">
         <v>7231</v>
       </c>
@@ -7815,7 +7815,7 @@
       <c r="BN33" s="122"/>
       <c r="BO33" s="122"/>
     </row>
-    <row r="34" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="48" t="s">
         <v>104</v>
       </c>
@@ -7832,7 +7832,7 @@
       <c r="J34" s="44"/>
       <c r="L34" s="122"/>
     </row>
-    <row r="35" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A35" s="58">
         <v>6767</v>
       </c>
@@ -7918,7 +7918,7 @@
       <c r="BN35" s="122"/>
       <c r="BO35" s="122"/>
     </row>
-    <row r="36" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="58">
         <v>6761</v>
       </c>
@@ -8004,7 +8004,7 @@
       <c r="BN36" s="122"/>
       <c r="BO36" s="122"/>
     </row>
-    <row r="37" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="58">
         <v>6764</v>
       </c>
@@ -8178,7 +8178,7 @@
       <c r="BN38" s="122"/>
       <c r="BO38" s="122"/>
     </row>
-    <row r="39" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="58">
         <v>7075</v>
       </c>
@@ -8264,7 +8264,7 @@
       <c r="BN39" s="122"/>
       <c r="BO39" s="122"/>
     </row>
-    <row r="40" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="58">
         <v>7083</v>
       </c>
@@ -8526,7 +8526,7 @@
       <c r="BN42" s="122"/>
       <c r="BO42" s="122"/>
     </row>
-    <row r="43" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="58">
         <v>7076</v>
       </c>
@@ -8788,7 +8788,7 @@
       <c r="BN45" s="122"/>
       <c r="BO45" s="122"/>
     </row>
-    <row r="46" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="58">
         <v>6661</v>
       </c>
@@ -8874,7 +8874,7 @@
       <c r="BN46" s="122"/>
       <c r="BO46" s="122"/>
     </row>
-    <row r="47" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="58">
         <v>6759</v>
       </c>
@@ -8960,7 +8960,7 @@
       <c r="BN47" s="122"/>
       <c r="BO47" s="122"/>
     </row>
-    <row r="48" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="58">
         <v>6762</v>
       </c>
@@ -9134,7 +9134,7 @@
       <c r="BN49" s="122"/>
       <c r="BO49" s="122"/>
     </row>
-    <row r="50" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="58">
         <v>7074</v>
       </c>
@@ -9308,7 +9308,7 @@
       <c r="BN51" s="122"/>
       <c r="BO51" s="122"/>
     </row>
-    <row r="52" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="58">
         <v>5819</v>
       </c>
@@ -9482,7 +9482,7 @@
       <c r="BN53" s="122"/>
       <c r="BO53" s="122"/>
     </row>
-    <row r="54" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="147">
         <v>7284</v>
       </c>
@@ -9660,7 +9660,7 @@
       <c r="BN55" s="122"/>
       <c r="BO55" s="122"/>
     </row>
-    <row r="56" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="58">
         <v>7601</v>
       </c>
@@ -9746,7 +9746,7 @@
       <c r="BN56" s="122"/>
       <c r="BO56" s="122"/>
     </row>
-    <row r="57" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="147">
         <v>7371</v>
       </c>
@@ -9834,7 +9834,7 @@
       <c r="BN57" s="122"/>
       <c r="BO57" s="122"/>
     </row>
-    <row r="58" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="58">
         <v>6837</v>
       </c>
@@ -9920,7 +9920,7 @@
       <c r="BN58" s="122"/>
       <c r="BO58" s="122"/>
     </row>
-    <row r="59" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="58">
         <v>7080</v>
       </c>
@@ -9950,7 +9950,7 @@
       <c r="J59" s="29"/>
       <c r="L59" s="122"/>
     </row>
-    <row r="60" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="58">
         <v>6724</v>
       </c>
@@ -10012,7 +10012,7 @@
       <c r="J61" s="29"/>
       <c r="L61" s="122"/>
     </row>
-    <row r="62" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="58">
         <v>6713</v>
       </c>
@@ -10074,7 +10074,7 @@
       <c r="J63" s="29"/>
       <c r="L63" s="122"/>
     </row>
-    <row r="64" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="58">
         <v>6602</v>
       </c>
@@ -10138,7 +10138,7 @@
       </c>
       <c r="L65" s="122"/>
     </row>
-    <row r="66" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="145">
         <v>7521</v>
       </c>
@@ -10170,7 +10170,7 @@
       </c>
       <c r="L66" s="122"/>
     </row>
-    <row r="67" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="58">
         <v>7073</v>
       </c>
@@ -10200,7 +10200,7 @@
       <c r="J67" s="29"/>
       <c r="L67" s="122"/>
     </row>
-    <row r="68" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="58">
         <v>7276</v>
       </c>
@@ -10262,7 +10262,7 @@
       <c r="J69" s="29"/>
       <c r="L69" s="122"/>
     </row>
-    <row r="70" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="58">
         <v>7044</v>
       </c>
@@ -10292,7 +10292,7 @@
       <c r="J70" s="29"/>
       <c r="L70" s="122"/>
     </row>
-    <row r="71" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="147">
         <v>7385</v>
       </c>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="L71" s="122"/>
     </row>
-    <row r="72" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A72" s="147">
         <v>7460</v>
       </c>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="L72" s="122"/>
     </row>
-    <row r="73" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="48" t="s">
         <v>104</v>
       </c>
@@ -10373,7 +10373,7 @@
       <c r="J73" s="44"/>
       <c r="L73" s="122"/>
     </row>
-    <row r="74" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A74" s="58">
         <v>6527</v>
       </c>
@@ -10403,7 +10403,7 @@
       <c r="J74" s="61"/>
       <c r="L74" s="122"/>
     </row>
-    <row r="75" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="58">
         <v>6550</v>
       </c>
@@ -10465,7 +10465,7 @@
       <c r="J76" s="29"/>
       <c r="L76" s="122"/>
     </row>
-    <row r="77" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="58">
         <v>7001</v>
       </c>
@@ -10495,7 +10495,7 @@
       <c r="J77" s="29"/>
       <c r="L77" s="122"/>
     </row>
-    <row r="78" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="58">
         <v>6608</v>
       </c>
@@ -10557,7 +10557,7 @@
       <c r="J79" s="29"/>
       <c r="L79" s="122"/>
     </row>
-    <row r="80" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A80" s="58">
         <v>6609</v>
       </c>
@@ -10587,7 +10587,7 @@
       <c r="J80" s="29"/>
       <c r="L80" s="122"/>
     </row>
-    <row r="81" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="48" t="s">
         <v>104</v>
       </c>
@@ -10604,7 +10604,7 @@
       <c r="J81" s="44"/>
       <c r="L81" s="122"/>
     </row>
-    <row r="82" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A82" s="145">
         <v>7564</v>
       </c>
@@ -10636,7 +10636,7 @@
       </c>
       <c r="L82" s="122"/>
     </row>
-    <row r="83" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="58">
         <v>7133</v>
       </c>
@@ -10666,7 +10666,7 @@
       <c r="J83" s="61"/>
       <c r="L83" s="122"/>
     </row>
-    <row r="84" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="58">
         <v>6946</v>
       </c>
@@ -10760,7 +10760,7 @@
       <c r="J86" s="61"/>
       <c r="L86" s="122"/>
     </row>
-    <row r="87" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="58">
         <v>7149</v>
       </c>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="L91" s="122"/>
     </row>
-    <row r="92" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="58">
         <v>6807</v>
       </c>
@@ -10952,7 +10952,7 @@
       <c r="J92" s="29"/>
       <c r="L92" s="122"/>
     </row>
-    <row r="93" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="58">
         <v>6787</v>
       </c>
@@ -11046,7 +11046,7 @@
       <c r="J95" s="29"/>
       <c r="L95" s="122"/>
     </row>
-    <row r="96" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="58">
         <v>7233</v>
       </c>
@@ -11108,7 +11108,7 @@
       <c r="J97" s="50"/>
       <c r="L97" s="122"/>
     </row>
-    <row r="98" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="58">
         <v>7177</v>
       </c>
@@ -11202,7 +11202,7 @@
       <c r="J100" s="50"/>
       <c r="L100" s="122"/>
     </row>
-    <row r="101" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="58">
         <v>7238</v>
       </c>
@@ -11232,7 +11232,7 @@
       <c r="J101" s="50"/>
       <c r="L101" s="122"/>
     </row>
-    <row r="102" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="147">
         <v>7237</v>
       </c>
@@ -11264,7 +11264,7 @@
       </c>
       <c r="L102" s="122"/>
     </row>
-    <row r="103" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="58">
         <v>7241</v>
       </c>
@@ -11294,7 +11294,7 @@
       <c r="J103" s="50"/>
       <c r="L103" s="122"/>
     </row>
-    <row r="104" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="58">
         <v>7332</v>
       </c>
@@ -11324,7 +11324,7 @@
       <c r="J104" s="50"/>
       <c r="L104" s="122"/>
     </row>
-    <row r="105" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="58">
         <v>7333</v>
       </c>
@@ -11354,7 +11354,7 @@
       <c r="J105" s="50"/>
       <c r="L105" s="122"/>
     </row>
-    <row r="106" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="145">
         <v>7608</v>
       </c>
@@ -11386,7 +11386,7 @@
       </c>
       <c r="L106" s="122"/>
     </row>
-    <row r="107" spans="1:67" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:67" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A107" s="145">
         <v>7610</v>
       </c>
@@ -11418,7 +11418,7 @@
       </c>
       <c r="L107" s="122"/>
     </row>
-    <row r="108" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="48" t="s">
         <v>104</v>
       </c>
@@ -11491,7 +11491,7 @@
       <c r="BN108" s="122"/>
       <c r="BO108" s="122"/>
     </row>
-    <row r="109" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A109" s="58">
         <v>614</v>
       </c>
@@ -11577,7 +11577,7 @@
       <c r="BN109" s="122"/>
       <c r="BO109" s="122"/>
     </row>
-    <row r="110" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="58">
         <v>3287</v>
       </c>
@@ -11663,7 +11663,7 @@
       <c r="BN110" s="122"/>
       <c r="BO110" s="122"/>
     </row>
-    <row r="111" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="58">
         <v>5708</v>
       </c>
@@ -11693,7 +11693,7 @@
       <c r="J111" s="29"/>
       <c r="L111" s="122"/>
     </row>
-    <row r="112" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="58">
         <v>4117</v>
       </c>
@@ -11723,7 +11723,7 @@
       <c r="J112" s="29"/>
       <c r="L112" s="122"/>
     </row>
-    <row r="113" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="58">
         <v>7316</v>
       </c>
@@ -11753,7 +11753,7 @@
       <c r="J113" s="29"/>
       <c r="L113" s="122"/>
     </row>
-    <row r="114" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="58">
         <v>7317</v>
       </c>
@@ -11783,7 +11783,7 @@
       <c r="J114" s="29"/>
       <c r="L114" s="122"/>
     </row>
-    <row r="115" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="58">
         <v>7143</v>
       </c>
@@ -11813,7 +11813,7 @@
       <c r="J115" s="29"/>
       <c r="L115" s="122"/>
     </row>
-    <row r="116" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="58">
         <v>7147</v>
       </c>
@@ -11843,7 +11843,7 @@
       <c r="J116" s="29"/>
       <c r="L116" s="122"/>
     </row>
-    <row r="117" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="58">
         <v>7456</v>
       </c>
@@ -11873,7 +11873,7 @@
       <c r="J117" s="29"/>
       <c r="L117" s="122"/>
     </row>
-    <row r="118" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="58">
         <v>7318</v>
       </c>
@@ -11935,7 +11935,7 @@
       <c r="J119" s="29"/>
       <c r="L119" s="122"/>
     </row>
-    <row r="120" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="58">
         <v>7364</v>
       </c>
@@ -11965,7 +11965,7 @@
       <c r="J120" s="29"/>
       <c r="L120" s="122"/>
     </row>
-    <row r="121" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="58">
         <v>7383</v>
       </c>
@@ -12027,7 +12027,7 @@
       <c r="J122" s="29"/>
       <c r="L122" s="122"/>
     </row>
-    <row r="123" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="58">
         <v>4993</v>
       </c>
@@ -12057,7 +12057,7 @@
       <c r="J123" s="29"/>
       <c r="L123" s="122"/>
     </row>
-    <row r="124" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="58">
         <v>6937</v>
       </c>
@@ -12087,7 +12087,7 @@
       <c r="J124" s="29"/>
       <c r="L124" s="122"/>
     </row>
-    <row r="125" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="58">
         <v>5483</v>
       </c>
@@ -12149,7 +12149,7 @@
       <c r="J126" s="29"/>
       <c r="L126" s="122"/>
     </row>
-    <row r="127" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="58">
         <v>6832</v>
       </c>
@@ -12179,7 +12179,7 @@
       <c r="J127" s="29"/>
       <c r="L127" s="122"/>
     </row>
-    <row r="128" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="58">
         <v>7299</v>
       </c>
@@ -12209,7 +12209,7 @@
       <c r="J128" s="29"/>
       <c r="L128" s="122"/>
     </row>
-    <row r="129" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="58">
         <v>7386</v>
       </c>
@@ -12239,7 +12239,7 @@
       <c r="J129" s="29"/>
       <c r="L129" s="122"/>
     </row>
-    <row r="130" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="58">
         <v>5679</v>
       </c>
@@ -12301,7 +12301,7 @@
       <c r="J131" s="29"/>
       <c r="L131" s="122"/>
     </row>
-    <row r="132" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="145">
         <v>7613</v>
       </c>
@@ -12399,7 +12399,7 @@
       <c r="J134" s="29"/>
       <c r="L134" s="122"/>
     </row>
-    <row r="135" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="58">
         <v>6222</v>
       </c>
@@ -12429,7 +12429,7 @@
       <c r="J135" s="29"/>
       <c r="L135" s="122"/>
     </row>
-    <row r="136" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="147">
         <v>6834</v>
       </c>
@@ -12461,7 +12461,7 @@
       </c>
       <c r="L136" s="122"/>
     </row>
-    <row r="137" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="147">
         <v>6965</v>
       </c>
@@ -12493,7 +12493,7 @@
       </c>
       <c r="L137" s="122"/>
     </row>
-    <row r="138" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="147">
         <v>6557</v>
       </c>
@@ -12525,7 +12525,7 @@
       </c>
       <c r="L138" s="122"/>
     </row>
-    <row r="139" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A139" s="145">
         <v>7626</v>
       </c>
@@ -12557,7 +12557,7 @@
       </c>
       <c r="L139" s="122"/>
     </row>
-    <row r="140" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="48" t="s">
         <v>104</v>
       </c>
@@ -12574,7 +12574,7 @@
       <c r="J140" s="44"/>
       <c r="L140" s="122"/>
     </row>
-    <row r="141" spans="1:67" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:67" ht="16.149999999999999" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A141" s="58">
         <v>6470</v>
       </c>
@@ -12604,7 +12604,7 @@
       <c r="J141" s="29"/>
       <c r="L141" s="122"/>
     </row>
-    <row r="142" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="58">
         <v>6495</v>
       </c>
@@ -12690,7 +12690,7 @@
       <c r="BN142" s="122"/>
       <c r="BO142" s="122"/>
     </row>
-    <row r="143" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="58">
         <v>5452</v>
       </c>
@@ -12776,7 +12776,7 @@
       <c r="BN143" s="122"/>
       <c r="BO143" s="122"/>
     </row>
-    <row r="144" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="58">
         <v>6866</v>
       </c>
@@ -12862,7 +12862,7 @@
       <c r="BN144" s="122"/>
       <c r="BO144" s="122"/>
     </row>
-    <row r="145" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="58">
         <v>6025</v>
       </c>
@@ -12948,7 +12948,7 @@
       <c r="BN145" s="122"/>
       <c r="BO145" s="122"/>
     </row>
-    <row r="146" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="58">
         <v>4584</v>
       </c>
@@ -13210,7 +13210,7 @@
       <c r="BN148" s="122"/>
       <c r="BO148" s="122"/>
     </row>
-    <row r="149" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="58">
         <v>7377</v>
       </c>
@@ -13296,7 +13296,7 @@
       <c r="BN149" s="122"/>
       <c r="BO149" s="122"/>
     </row>
-    <row r="150" spans="1:67" s="63" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:67" s="63" customFormat="1" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="58">
         <v>6925</v>
       </c>
@@ -13382,7 +13382,7 @@
       <c r="BN150" s="122"/>
       <c r="BO150" s="122"/>
     </row>
-    <row r="151" spans="1:67" s="63" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:67" s="63" customFormat="1" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="145">
         <v>7647</v>
       </c>
@@ -13470,7 +13470,7 @@
       <c r="BN151" s="122"/>
       <c r="BO151" s="122"/>
     </row>
-    <row r="152" spans="1:67" s="63" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:67" s="63" customFormat="1" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A152" s="145">
         <v>7651</v>
       </c>
@@ -13558,7 +13558,7 @@
       <c r="BN152" s="122"/>
       <c r="BO152" s="122"/>
     </row>
-    <row r="153" spans="1:67" s="63" customFormat="1" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:67" s="63" customFormat="1" ht="15.75" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="48" t="s">
         <v>104</v>
       </c>
@@ -13631,7 +13631,7 @@
       <c r="BN153" s="122"/>
       <c r="BO153" s="122"/>
     </row>
-    <row r="154" spans="1:67" s="63" customFormat="1" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:67" s="63" customFormat="1" ht="15.75" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A154" s="145">
         <v>7485</v>
       </c>
@@ -13719,7 +13719,7 @@
       <c r="BN154" s="122"/>
       <c r="BO154" s="122"/>
     </row>
-    <row r="155" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="48" t="s">
         <v>104</v>
       </c>
@@ -13736,7 +13736,7 @@
       <c r="J155" s="44"/>
       <c r="L155" s="122"/>
     </row>
-    <row r="156" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="58">
         <v>6620</v>
       </c>
@@ -13768,7 +13768,7 @@
       <c r="J156" s="29"/>
       <c r="L156" s="122"/>
     </row>
-    <row r="157" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="58">
         <v>7187</v>
       </c>
@@ -13798,7 +13798,7 @@
       <c r="J157" s="29"/>
       <c r="L157" s="122"/>
     </row>
-    <row r="158" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="145">
         <v>6008</v>
       </c>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="L158" s="122"/>
     </row>
-    <row r="159" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="58">
         <v>7090</v>
       </c>
@@ -13892,7 +13892,7 @@
       <c r="J160" s="29"/>
       <c r="L160" s="122"/>
     </row>
-    <row r="161" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="58">
         <v>6279</v>
       </c>
@@ -13922,7 +13922,7 @@
       <c r="J161" s="29"/>
       <c r="L161" s="122"/>
     </row>
-    <row r="162" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="58">
         <v>7092</v>
       </c>
@@ -13952,7 +13952,7 @@
       <c r="J162" s="29"/>
       <c r="L162" s="122"/>
     </row>
-    <row r="163" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="58">
         <v>6448</v>
       </c>
@@ -13982,7 +13982,7 @@
       <c r="J163" s="29"/>
       <c r="L163" s="122"/>
     </row>
-    <row r="164" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="58">
         <v>6754</v>
       </c>
@@ -14012,7 +14012,7 @@
       <c r="J164" s="29"/>
       <c r="L164" s="122"/>
     </row>
-    <row r="165" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="58">
         <v>6208</v>
       </c>
@@ -14044,7 +14044,7 @@
       <c r="J165" s="29"/>
       <c r="L165" s="122"/>
     </row>
-    <row r="166" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="58">
         <v>6228</v>
       </c>
@@ -14074,7 +14074,7 @@
       <c r="J166" s="29"/>
       <c r="L166" s="122"/>
     </row>
-    <row r="167" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="145">
         <v>7612</v>
       </c>
@@ -29370,7 +29370,13 @@
       <c r="J1692" s="21"/>
     </row>
   </sheetData>
-  <autoFilter ref="A9:J168" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A9:J168" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="E1:J1"/>
     <mergeCell ref="G3:J3"/>
